--- a/artfynd/Gubbmyran artfynd.xlsx
+++ b/artfynd/Gubbmyran artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>301114</v>
+        <v>56606354</v>
       </c>
       <c r="B2" t="n">
-        <v>91241</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
+          <t>Gubbträskbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659154</v>
+        <v>657939</v>
       </c>
       <c r="R2" t="n">
-        <v>7140474</v>
+        <v>7142126</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,31 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>435703</v>
+        <v>56606353</v>
       </c>
       <c r="B3" t="n">
-        <v>75080</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
+          <t>Gubbträskbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659052</v>
+        <v>657887</v>
       </c>
       <c r="R3" t="n">
-        <v>7140732</v>
+        <v>7142186</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -842,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,41 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>granurskog!</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>björkhögstubbe</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>383870</v>
+        <v>56606355</v>
       </c>
       <c r="B4" t="n">
-        <v>82792</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
+          <t>Gubbträskbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659313</v>
+        <v>657939</v>
       </c>
       <c r="R4" t="n">
-        <v>7140616</v>
+        <v>7142126</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,31 +950,16 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>granurskog!</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1004,7 +969,7 @@
         <v>78576548</v>
       </c>
       <c r="B5" t="n">
-        <v>75080</v>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>159073</v>
+        <v>78576549</v>
       </c>
       <c r="B6" t="n">
-        <v>88654</v>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
+          <t>Gubbträskbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659294</v>
+        <v>658419</v>
       </c>
       <c r="R6" t="n">
-        <v>7140485</v>
+        <v>7140063</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2019-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2019-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1179,58 +1144,48 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>granurskog!</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Emil Larsson, Anna Hallmén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16944544</v>
+        <v>16945035</v>
       </c>
       <c r="B7" t="n">
-        <v>91259</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659093</v>
+        <v>658599</v>
       </c>
       <c r="R7" t="n">
-        <v>7140574</v>
+        <v>7140533</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1297,14 +1252,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>låga</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1322,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16944494</v>
+        <v>104405663</v>
       </c>
       <c r="B8" t="n">
-        <v>91263</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,37 +1283,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gubbträskbäcken, Ly lm</t>
+          <t>Gubbträskliden, Lycksele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659287</v>
+        <v>658140</v>
       </c>
       <c r="R8" t="n">
-        <v>7140236</v>
+        <v>7140337</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,12 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,41 +1358,30 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>435702</v>
+        <v>16944818</v>
       </c>
       <c r="B9" t="n">
-        <v>75080</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,37 +1389,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
+          <t>Gubbträskbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659294</v>
+        <v>658478</v>
       </c>
       <c r="R9" t="n">
-        <v>7140485</v>
+        <v>7141159</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1499,12 +1443,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,40 +1460,40 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>granurskog!</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>mkt grov björk!</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16944817</v>
+        <v>16944820</v>
       </c>
       <c r="B10" t="n">
-        <v>91541</v>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,12 +1510,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>659116</v>
+        <v>658614</v>
       </c>
       <c r="R10" t="n">
-        <v>7140544</v>
+        <v>7140848</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1658,32 +1602,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16944597</v>
+        <v>16945063</v>
       </c>
       <c r="B11" t="n">
-        <v>91446</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>659116</v>
+        <v>658495</v>
       </c>
       <c r="R11" t="n">
-        <v>7140544</v>
+        <v>7141277</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,14 +1714,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>333432</v>
+        <v>16944540</v>
       </c>
       <c r="B12" t="n">
-        <v>91259</v>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1801,17 +1745,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
+          <t>Gubbträskbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>659084</v>
+        <v>658488</v>
       </c>
       <c r="R12" t="n">
-        <v>7140513</v>
+        <v>7141158</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1835,12 +1779,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,40 +1796,45 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>granurskog</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>låga</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Picea abies # låga</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16944596</v>
+        <v>16944542</v>
       </c>
       <c r="B13" t="n">
-        <v>91446</v>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,21 +1842,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>659472</v>
+        <v>658587</v>
       </c>
       <c r="R13" t="n">
-        <v>7140406</v>
+        <v>7140885</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1974,9 +1923,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # låga</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1994,48 +1948,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>375064</v>
+        <v>16944371</v>
       </c>
       <c r="B14" t="n">
-        <v>91699</v>
+        <v>92333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
+          <t>Gubbträskbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>659084</v>
+        <v>658479</v>
       </c>
       <c r="R14" t="n">
-        <v>7140513</v>
+        <v>7141161</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2059,12 +2013,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,40 +2030,40 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>granurskog</t>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>174574</v>
+        <v>16944597</v>
       </c>
       <c r="B15" t="n">
-        <v>78343</v>
+        <v>92123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,37 +2071,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>498</v>
+        <v>48</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
+          <t>Gubbträskbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>659052</v>
+        <v>659116</v>
       </c>
       <c r="R15" t="n">
-        <v>7140732</v>
+        <v>7140544</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2171,12 +2125,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,40 +2142,40 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>granurskog!</t>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>urgammal gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16944492</v>
+        <v>16945122</v>
       </c>
       <c r="B16" t="n">
-        <v>91263</v>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,21 +2183,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2253,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>658567</v>
+        <v>658643</v>
       </c>
       <c r="R16" t="n">
-        <v>7140413</v>
+        <v>7140575</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2299,21 +2253,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2330,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16944820</v>
+        <v>16944817</v>
       </c>
       <c r="B17" t="n">
-        <v>91541</v>
+        <v>92208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,12 +2289,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2365,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>658614</v>
+        <v>659116</v>
       </c>
       <c r="R17" t="n">
-        <v>7140848</v>
+        <v>7140544</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2442,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16944818</v>
+        <v>301114</v>
       </c>
       <c r="B18" t="n">
-        <v>91541</v>
+        <v>91905</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,37 +2392,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gubbträskbäcken, Ly lm</t>
+          <t>Sydost Gubbmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>658478</v>
+        <v>659154</v>
       </c>
       <c r="R18" t="n">
-        <v>7141159</v>
+        <v>7140474</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2507,12 +2446,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,40 +2463,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16945122</v>
+        <v>403105</v>
       </c>
       <c r="B19" t="n">
-        <v>79012</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2565,37 +2494,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gubbträskbäcken, Ly lm</t>
+          <t>Sydost Gubbmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>658643</v>
+        <v>659054</v>
       </c>
       <c r="R19" t="n">
-        <v>7140575</v>
+        <v>7140493</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2619,12 +2548,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,64 +2564,79 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>granurskog</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>56606353</v>
+        <v>333432</v>
       </c>
       <c r="B20" t="n">
-        <v>91245</v>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gubbträskbäcken, Ly lm</t>
+          <t>Sydost Gubbmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>657887</v>
+        <v>659084</v>
       </c>
       <c r="R20" t="n">
-        <v>7142186</v>
+        <v>7140513</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2716,12 +2660,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,48 +2676,63 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>granurskog</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>56606354</v>
+        <v>16944543</v>
       </c>
       <c r="B21" t="n">
-        <v>91541</v>
+        <v>91923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2783,13 +2742,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>657939</v>
+        <v>658644</v>
       </c>
       <c r="R21" t="n">
-        <v>7142126</v>
+        <v>7140549</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2829,64 +2788,84 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies # låga</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>91581</v>
+        <v>16944544</v>
       </c>
       <c r="B22" t="n">
-        <v>77944</v>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>314</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
+          <t>Gubbträskbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>659294</v>
+        <v>659093</v>
       </c>
       <c r="R22" t="n">
-        <v>7140485</v>
+        <v>7140574</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2910,12 +2889,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2927,40 +2906,45 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>granurskog!</t>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>låga</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>under grenbas</t>
+          <t>Picea abies # låga</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16945061</v>
+        <v>375064</v>
       </c>
       <c r="B23" t="n">
-        <v>91245</v>
+        <v>92369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2968,37 +2952,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gubbträskbäcken, Ly lm</t>
+          <t>Sydost Gubbmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>659126</v>
+        <v>659084</v>
       </c>
       <c r="R23" t="n">
-        <v>7140713</v>
+        <v>7140513</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3022,12 +3006,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3039,78 +3023,78 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>granurskog</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>16944542</v>
+        <v>1860102</v>
       </c>
       <c r="B24" t="n">
-        <v>91259</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gubbträskbäcken, Ly lm</t>
+          <t>Sydost Gubbmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>658587</v>
+        <v>659054</v>
       </c>
       <c r="R24" t="n">
-        <v>7140885</v>
+        <v>7140493</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3134,12 +3118,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-11-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>draperade träd!</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3151,67 +3140,62 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>låga</t>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>granurskog!</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # låga</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>403105</v>
+        <v>174574</v>
       </c>
       <c r="B25" t="n">
-        <v>91245</v>
+        <v>78686</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3221,10 +3205,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>659054</v>
+        <v>659052</v>
       </c>
       <c r="R25" t="n">
-        <v>7140493</v>
+        <v>7140732</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3275,12 +3259,12 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>granurskog</t>
+          <t>granurskog!</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>urgammal gran</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3298,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>16944491</v>
+        <v>212822</v>
       </c>
       <c r="B26" t="n">
-        <v>91263</v>
+        <v>92208</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3309,37 +3293,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gubbträskbäcken, Ly lm</t>
+          <t>Sydost Gubbmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>658680</v>
+        <v>659052</v>
       </c>
       <c r="R26" t="n">
-        <v>7141084</v>
+        <v>7140732</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3363,12 +3347,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3380,40 +3364,40 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>granurskog!</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>björkstubbe</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>16944540</v>
+        <v>16944819</v>
       </c>
       <c r="B27" t="n">
-        <v>91259</v>
+        <v>92208</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,21 +3405,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3445,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>658488</v>
+        <v>659126</v>
       </c>
       <c r="R27" t="n">
-        <v>7141158</v>
+        <v>7140713</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3502,14 +3486,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>låga</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3527,10 +3506,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>56606355</v>
+        <v>16945061</v>
       </c>
       <c r="B28" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3562,13 +3541,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>657939</v>
+        <v>659126</v>
       </c>
       <c r="R28" t="n">
-        <v>7142126</v>
+        <v>7140713</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3608,48 +3587,63 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16944371</v>
+        <v>16944541</v>
       </c>
       <c r="B29" t="n">
-        <v>91655</v>
+        <v>91923</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4217</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3659,10 +3653,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>658479</v>
+        <v>659057</v>
       </c>
       <c r="R29" t="n">
-        <v>7141161</v>
+        <v>7140585</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3716,9 +3710,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # låga</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3736,48 +3735,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16945035</v>
+        <v>435703</v>
       </c>
       <c r="B30" t="n">
-        <v>91942</v>
+        <v>83312</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>1467</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gubbträskbäcken, Ly lm</t>
+          <t>Sydost Gubbmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>658599</v>
+        <v>659052</v>
       </c>
       <c r="R30" t="n">
-        <v>7140533</v>
+        <v>7140732</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3801,12 +3800,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3818,62 +3817,62 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>granurskog!</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>78576549</v>
+        <v>16944596</v>
       </c>
       <c r="B31" t="n">
-        <v>75080</v>
+        <v>92123</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1467</v>
+        <v>48</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3883,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>658419</v>
+        <v>659472</v>
       </c>
       <c r="R31" t="n">
-        <v>7140063</v>
+        <v>7140406</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3913,12 +3912,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2019-06-12</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2019-06-12</t>
+          <t>2014-08-13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,64 +3928,79 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emil Larsson, Anna Hallmén</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16944543</v>
+        <v>91581</v>
       </c>
       <c r="B32" t="n">
-        <v>91259</v>
+        <v>78350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gubbträskbäcken, Ly lm</t>
+          <t>Sydost Gubbmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>658644</v>
+        <v>659294</v>
       </c>
       <c r="R32" t="n">
-        <v>7140549</v>
+        <v>7140485</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4010,12 +4024,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4027,45 +4041,40 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>låga</t>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>granurskog!</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies # låga</t>
+          <t>under grenbas</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>78576533</v>
+        <v>159073</v>
       </c>
       <c r="B33" t="n">
-        <v>91263</v>
+        <v>89292</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4073,37 +4082,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gubbträskbäcken, Ly lm</t>
+          <t>Sydost Gubbmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>658435</v>
+        <v>659294</v>
       </c>
       <c r="R33" t="n">
-        <v>7139966</v>
+        <v>7140485</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4127,12 +4136,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2019-06-12</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2019-06-12</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4143,26 +4152,36 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>granurskog!</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emil Larsson, Anna Hallmén</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16944541</v>
+        <v>435702</v>
       </c>
       <c r="B34" t="n">
-        <v>91259</v>
+        <v>83312</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,37 +4189,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gubbträskbäcken, Ly lm</t>
+          <t>Sydost Gubbmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>659057</v>
+        <v>659294</v>
       </c>
       <c r="R34" t="n">
-        <v>7140585</v>
+        <v>7140485</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4224,12 +4243,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4241,45 +4260,40 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>låga</t>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>granurskog!</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies # låga</t>
+          <t>mkt grov björk!</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16944819</v>
+        <v>383870</v>
       </c>
       <c r="B35" t="n">
-        <v>91541</v>
+        <v>83173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4287,37 +4301,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gubbträskbäcken, Ly lm</t>
+          <t>Sydost Gubbmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>659126</v>
+        <v>659313</v>
       </c>
       <c r="R35" t="n">
-        <v>7140713</v>
+        <v>7140616</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4341,12 +4355,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2014-08-13</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4358,802 +4372,33 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>granurskog!</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>gammal gran</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>16944493</v>
-      </c>
-      <c r="B36" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Gubbträskbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>658731</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7140327</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2014-08-13</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2014-08-13</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>1860102</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78980</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>659054</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7140493</v>
-      </c>
-      <c r="S37" t="n">
-        <v>25</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2003-08-01</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2003-11-01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>draperade träd!</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>granurskog!</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>1540140</v>
-      </c>
-      <c r="B38" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>659084</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7140513</v>
-      </c>
-      <c r="S38" t="n">
-        <v>25</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2003-08-01</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2003-11-01</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>granurskog</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>1540141</v>
-      </c>
-      <c r="B39" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>659313</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7140616</v>
-      </c>
-      <c r="S39" t="n">
-        <v>50</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2003-08-01</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2003-11-01</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>granurskog!</t>
-        </is>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>78576534</v>
-      </c>
-      <c r="B40" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Gubbträskbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>658434</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7139992</v>
-      </c>
-      <c r="S40" t="n">
-        <v>5</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2019-06-12</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Emil Larsson, Anna Hallmén</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>212822</v>
-      </c>
-      <c r="B41" t="n">
-        <v>91541</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>658</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Sydost Gubbmyran, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>659052</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7140732</v>
-      </c>
-      <c r="S41" t="n">
-        <v>50</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2003-08-01</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2003-11-01</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>granurskog!</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>björkstubbe</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>16944490</v>
-      </c>
-      <c r="B42" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Gubbträskbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>658738</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7141073</v>
-      </c>
-      <c r="S42" t="n">
-        <v>5</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2014-08-13</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2014-08-13</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
